--- a/docs/planning/Wysker_Watch_Launch_Plan.xlsx
+++ b/docs/planning/Wysker_Watch_Launch_Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\whisker-watch-supabase\docs\planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E5A5F8-6AF9-4B06-A574-C7079966610F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B71B355-990A-44F1-A571-0B9F0B69FF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,12 +324,6 @@
     <t>Confirm before relying on it for launch week.</t>
   </si>
   <si>
-    <t>Shutterstock sourcing for real pet photography</t>
-  </si>
-  <si>
-    <t>Preferred over AI-generated images. Confirm MCP connector activation.</t>
-  </si>
-  <si>
     <t>Business Readiness</t>
   </si>
   <si>
@@ -865,6 +859,12 @@
   </si>
   <si>
     <t>Currently an unbuilt placeholder — decide before Alpha whether it ships hidden or stays as-is.</t>
+  </si>
+  <si>
+    <t>Add automated test coverage for co-owner save conflicts via the new Check-In History calendar (spec 0060)</t>
+  </si>
+  <si>
+    <t>The underlying protection (spec 0043's conflict detection) already applies to every save through DailyCheckInSheet, including this new entry point — this is about proving it with an automated test, which needs a dedicated second co-owner test fixture account that doesn't exist yet. Borderline edge case (two co-owners editing the same past day at the same time); address after App Store launch unless it actually happens in production first.</t>
   </si>
   <si>
     <t>Summary</t>
@@ -1443,19 +1443,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1466,16 +1453,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1490,11 +1475,26 @@
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2067,20 +2067,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DDAB-474B-9348-4DB5B2407196}"/>
+              <c16:uniqueId val="{00000000-932A-4290-8EFB-1851F1B94823}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2405,7 +2405,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="92" t="s">
         <v>281</v>
       </c>
       <c r="B1" s="69"/>
@@ -2439,7 +2439,7 @@
       <c r="N2" s="69"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="89" t="s">
         <v>282</v>
       </c>
       <c r="B3" s="69"/>
@@ -2473,93 +2473,93 @@
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="85" t="s">
         <v>283</v>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="69"/>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="90" t="s">
         <v>284</v>
       </c>
       <c r="E5" s="69"/>
       <c r="F5" s="69"/>
-      <c r="G5" s="91" t="s">
+      <c r="G5" s="86" t="s">
         <v>285</v>
       </c>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="77" t="s">
+      <c r="J5" s="93" t="s">
         <v>286</v>
       </c>
       <c r="K5" s="69"/>
       <c r="L5" s="69"/>
-      <c r="M5" s="95" t="s">
+      <c r="M5" s="84" t="s">
         <v>287</v>
       </c>
       <c r="N5" s="69"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="78">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,"Complete")+COUNTIF('Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIF('Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>114</v>
-      </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="78">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,"Complete")</f>
-        <v>20</v>
-      </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="78">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,"In Progress")</f>
-        <v>3</v>
-      </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="78">
-        <f>COUNTIFS('Launch Plan'!$L$5:$L$127,"Yes",'Launch Plan'!$K$5:$K$127,"&lt;&gt;Complete")</f>
+      <c r="A6" s="73">
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,"Complete")+COUNTIF('Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIF('Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>113</v>
+      </c>
+      <c r="B6" s="74"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="73">
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,"Complete")</f>
+        <v>22</v>
+      </c>
+      <c r="E6" s="74"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="73">
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,"In Progress")</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="74"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="73">
+        <f>COUNTIFS('Launch Plan'!$L$5:$L$126,"Yes",'Launch Plan'!$K$5:$K$126,"&lt;&gt;Complete")</f>
         <v>35</v>
       </c>
-      <c r="K6" s="79"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="78" t="str">
-        <f>COUNTIFS('Launch Plan'!$E$5:$E$127,"GATE",'Launch Plan'!$K$5:$K$127,"Complete")&amp;" / "&amp;COUNTIF('Launch Plan'!$E$5:$E$127,"GATE")</f>
+      <c r="K6" s="74"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="73" t="str">
+        <f>COUNTIFS('Launch Plan'!$E$5:$E$126,"GATE",'Launch Plan'!$K$5:$K$126,"Complete")&amp;" / "&amp;COUNTIF('Launch Plan'!$E$5:$E$126,"GATE")</f>
         <v>0 / 15</v>
       </c>
-      <c r="N6" s="80"/>
+      <c r="N6" s="75"/>
     </row>
     <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="81"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="69"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="81"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="76"/>
       <c r="E7" s="69"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="81"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="76"/>
       <c r="H7" s="69"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="81"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="76"/>
       <c r="K7" s="69"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="82"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="83"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="85"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="80"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -2578,7 +2578,7 @@
       <c r="N9" s="8"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="87" t="s">
         <v>288</v>
       </c>
       <c r="B10" s="69"/>
@@ -2587,7 +2587,7 @@
       <c r="E10" s="69"/>
       <c r="F10" s="69"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="92" t="s">
+      <c r="H10" s="87" t="s">
         <v>289</v>
       </c>
       <c r="I10" s="69"/>
@@ -2652,8 +2652,8 @@
         <v>21</v>
       </c>
       <c r="B13" s="12">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,A13)</f>
-        <v>20</v>
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,A13)</f>
+        <v>22</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2664,19 +2664,19 @@
         <v>15</v>
       </c>
       <c r="I13" s="23">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>34</v>
       </c>
       <c r="J13" s="23">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>15</v>
       </c>
       <c r="K13" s="23">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="L13" s="23">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H13,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H13,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>18</v>
       </c>
       <c r="M13" s="26">
@@ -2693,8 +2693,8 @@
         <v>77</v>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,A14)</f>
-        <v>3</v>
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,A14)</f>
+        <v>2</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -2705,19 +2705,19 @@
         <v>46</v>
       </c>
       <c r="I14" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="J14" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>4</v>
       </c>
       <c r="K14" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L14" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H14,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H14,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="M14" s="27">
@@ -2734,8 +2734,8 @@
         <v>70</v>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('Launch Plan'!$K$5:$K$127,A15)</f>
-        <v>91</v>
+        <f>COUNTIF('Launch Plan'!$K$5:$K$126,A15)</f>
+        <v>89</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2746,19 +2746,19 @@
         <v>86</v>
       </c>
       <c r="I15" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="J15" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K15" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L15" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H15,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H15,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="M15" s="27">
@@ -2782,20 +2782,20 @@
         <v>92</v>
       </c>
       <c r="I16" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>9</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>8</v>
       </c>
       <c r="J16" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K16" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="L16" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H16,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>8</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H16,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>7</v>
       </c>
       <c r="M16" s="27">
         <f t="shared" si="0"/>
@@ -2815,31 +2815,31 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I17" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>9</v>
       </c>
       <c r="J17" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"Complete")</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="24">
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
-        <v>1</v>
-      </c>
       <c r="L17" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H17,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H17,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>8</v>
       </c>
       <c r="M17" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N17" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>MOVING</v>
+        <v>PARTIAL</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -2851,27 +2851,27 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I18" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>14</v>
       </c>
       <c r="J18" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"Complete")</f>
-        <v>1</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"Complete")</f>
+        <v>2</v>
       </c>
       <c r="K18" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L18" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H18,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>13</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H18,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>12</v>
       </c>
       <c r="M18" s="27">
         <f t="shared" si="0"/>
-        <v>7.1428571428571425E-2</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="N18" s="14" t="str">
         <f t="shared" si="1"/>
@@ -2887,22 +2887,22 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I19" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>12</v>
       </c>
       <c r="J19" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K19" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L19" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H19,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H19,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>12</v>
       </c>
       <c r="M19" s="27">
@@ -2923,22 +2923,22 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I20" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>10</v>
       </c>
       <c r="J20" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K20" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L20" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H20,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H20,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>10</v>
       </c>
       <c r="M20" s="27">
@@ -2959,22 +2959,22 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I21" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>19</v>
       </c>
       <c r="J21" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K21" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L21" s="24">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H21,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H21,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>19</v>
       </c>
       <c r="M21" s="27">
@@ -2995,22 +2995,22 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I22" s="25">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="J22" s="25">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="K22" s="25">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="L22" s="25">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,H22,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,H22,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="M22" s="28">
@@ -3071,7 +3071,7 @@
       <c r="N25" s="8"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="73" t="s">
+      <c r="A26" s="91" t="s">
         <v>294</v>
       </c>
       <c r="B26" s="69"/>
@@ -3089,7 +3089,7 @@
       <c r="N26" s="69"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="88" t="s">
         <v>295</v>
       </c>
       <c r="B27" s="69"/>
@@ -3126,18 +3126,18 @@
       <c r="A29" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="B29" s="87" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="75"/>
+      <c r="B29" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82"/>
+      <c r="I29" s="82"/>
+      <c r="J29" s="82"/>
+      <c r="K29" s="82"/>
       <c r="L29" s="30" t="s">
         <v>12</v>
       </c>
@@ -3150,28 +3150,28 @@
     </row>
     <row r="30" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="str">
-        <f>'Launch Plan'!A72</f>
+        <f>'Launch Plan'!A71</f>
         <v>Alpha</v>
       </c>
-      <c r="B30" s="94" t="str">
-        <f>'Launch Plan'!D72</f>
+      <c r="B30" s="83" t="str">
+        <f>'Launch Plan'!D71</f>
         <v>PWA GATE: Alpha Habit-Stickiness passed</v>
       </c>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
       <c r="L30" s="38" t="str">
-        <f>'Launch Plan'!K72</f>
+        <f>'Launch Plan'!K71</f>
         <v>Not Started</v>
       </c>
       <c r="M30" s="38" t="str">
-        <f>'Launch Plan'!L72</f>
+        <f>'Launch Plan'!L71</f>
         <v>Yes</v>
       </c>
       <c r="N30" s="38" t="str">
@@ -3181,28 +3181,28 @@
     </row>
     <row r="31" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="36" t="str">
-        <f>'Launch Plan'!A73</f>
+        <f>'Launch Plan'!A72</f>
         <v>PWA</v>
       </c>
-      <c r="B31" s="74" t="str">
-        <f>'Launch Plan'!D73</f>
+      <c r="B31" s="81" t="str">
+        <f>'Launch Plan'!D72</f>
         <v>PWA GATE: No Critical bugs open</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
       <c r="L31" s="39" t="str">
-        <f>'Launch Plan'!K73</f>
+        <f>'Launch Plan'!K72</f>
         <v>Not Started</v>
       </c>
       <c r="M31" s="39" t="str">
-        <f>'Launch Plan'!L73</f>
+        <f>'Launch Plan'!L72</f>
         <v>Yes</v>
       </c>
       <c r="N31" s="39" t="str">
@@ -3212,28 +3212,28 @@
     </row>
     <row r="32" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="36" t="str">
-        <f>'Launch Plan'!A74</f>
+        <f>'Launch Plan'!A73</f>
         <v>PWA</v>
       </c>
-      <c r="B32" s="74" t="str">
-        <f>'Launch Plan'!D74</f>
+      <c r="B32" s="81" t="str">
+        <f>'Launch Plan'!D73</f>
         <v>PWA GATE: Regression passed (real, non-zero test count)</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
       <c r="L32" s="39" t="str">
-        <f>'Launch Plan'!K74</f>
+        <f>'Launch Plan'!K73</f>
         <v>Not Started</v>
       </c>
       <c r="M32" s="39" t="str">
-        <f>'Launch Plan'!L74</f>
+        <f>'Launch Plan'!L73</f>
         <v>Yes</v>
       </c>
       <c r="N32" s="39" t="str">
@@ -3243,28 +3243,28 @@
     </row>
     <row r="33" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="36" t="str">
-        <f>'Launch Plan'!A75</f>
+        <f>'Launch Plan'!A74</f>
         <v>PWA</v>
       </c>
-      <c r="B33" s="74" t="str">
-        <f>'Launch Plan'!D75</f>
+      <c r="B33" s="81" t="str">
+        <f>'Launch Plan'!D74</f>
         <v>PWA GATE: Accessibility passed</v>
       </c>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
       <c r="L33" s="39" t="str">
-        <f>'Launch Plan'!K75</f>
+        <f>'Launch Plan'!K74</f>
         <v>Not Started</v>
       </c>
       <c r="M33" s="39" t="str">
-        <f>'Launch Plan'!L75</f>
+        <f>'Launch Plan'!L74</f>
         <v>Yes</v>
       </c>
       <c r="N33" s="39" t="str">
@@ -3274,28 +3274,28 @@
     </row>
     <row r="34" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="36" t="str">
-        <f>'Launch Plan'!A76</f>
+        <f>'Launch Plan'!A75</f>
         <v>PWA</v>
       </c>
-      <c r="B34" s="74" t="str">
-        <f>'Launch Plan'!D76</f>
+      <c r="B34" s="81" t="str">
+        <f>'Launch Plan'!D75</f>
         <v>PWA GATE: Privacy Policy hosted AND deletion confirmed working</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
       <c r="L34" s="39" t="str">
-        <f>'Launch Plan'!K76</f>
+        <f>'Launch Plan'!K75</f>
         <v>Not Started</v>
       </c>
       <c r="M34" s="39" t="str">
-        <f>'Launch Plan'!L76</f>
+        <f>'Launch Plan'!L75</f>
         <v>Yes</v>
       </c>
       <c r="N34" s="39" t="str">
@@ -3305,28 +3305,28 @@
     </row>
     <row r="35" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="36" t="str">
-        <f>'Launch Plan'!A77</f>
+        <f>'Launch Plan'!A76</f>
         <v>PWA</v>
       </c>
-      <c r="B35" s="74" t="str">
-        <f>'Launch Plan'!D77</f>
+      <c r="B35" s="81" t="str">
+        <f>'Launch Plan'!D76</f>
         <v>PWA GATE: Support inbox staffed and monitored</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
       <c r="L35" s="39" t="str">
-        <f>'Launch Plan'!K77</f>
+        <f>'Launch Plan'!K76</f>
         <v>Not Started</v>
       </c>
       <c r="M35" s="39" t="str">
-        <f>'Launch Plan'!L77</f>
+        <f>'Launch Plan'!L76</f>
         <v>Yes</v>
       </c>
       <c r="N35" s="39" t="str">
@@ -3336,28 +3336,28 @@
     </row>
     <row r="36" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="36" t="str">
-        <f>'Launch Plan'!A78</f>
+        <f>'Launch Plan'!A77</f>
         <v>PWA</v>
       </c>
-      <c r="B36" s="74" t="str">
-        <f>'Launch Plan'!D78</f>
+      <c r="B36" s="81" t="str">
+        <f>'Launch Plan'!D77</f>
         <v>PWA GATE: Analytics clean (no undercounts, rollups un-blended)</v>
       </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
       <c r="L36" s="39" t="str">
-        <f>'Launch Plan'!K78</f>
+        <f>'Launch Plan'!K77</f>
         <v>Not Started</v>
       </c>
       <c r="M36" s="39" t="str">
-        <f>'Launch Plan'!L78</f>
+        <f>'Launch Plan'!L77</f>
         <v>Yes</v>
       </c>
       <c r="N36" s="39" t="str">
@@ -3367,28 +3367,28 @@
     </row>
     <row r="37" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="36" t="str">
-        <f>'Launch Plan'!A79</f>
+        <f>'Launch Plan'!A78</f>
         <v>PWA</v>
       </c>
-      <c r="B37" s="74" t="str">
-        <f>'Launch Plan'!D79</f>
+      <c r="B37" s="81" t="str">
+        <f>'Launch Plan'!D78</f>
         <v>PWA GATE: Real-User Acquisition floor met, or explicit conscious-small-launch decision recorded</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="75"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="75"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
       <c r="L37" s="39" t="str">
-        <f>'Launch Plan'!K79</f>
+        <f>'Launch Plan'!K78</f>
         <v>Not Started</v>
       </c>
       <c r="M37" s="39" t="str">
-        <f>'Launch Plan'!L79</f>
+        <f>'Launch Plan'!L78</f>
         <v>Yes</v>
       </c>
       <c r="N37" s="39" t="str">
@@ -3398,28 +3398,28 @@
     </row>
     <row r="38" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="str">
-        <f>'Launch Plan'!A80</f>
+        <f>'Launch Plan'!A79</f>
         <v>PWA</v>
       </c>
-      <c r="B38" s="74" t="str">
-        <f>'Launch Plan'!D80</f>
+      <c r="B38" s="81" t="str">
+        <f>'Launch Plan'!D79</f>
         <v>PWA GATE: Founder approval, in writing, same day</v>
       </c>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
       <c r="L38" s="39" t="str">
-        <f>'Launch Plan'!K80</f>
+        <f>'Launch Plan'!K79</f>
         <v>Not Started</v>
       </c>
       <c r="M38" s="39" t="str">
-        <f>'Launch Plan'!L80</f>
+        <f>'Launch Plan'!L79</f>
         <v>Yes</v>
       </c>
       <c r="N38" s="39" t="str">
@@ -3429,28 +3429,28 @@
     </row>
     <row r="39" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="36" t="str">
-        <f>'Launch Plan'!A81</f>
+        <f>'Launch Plan'!A80</f>
         <v>PWA</v>
       </c>
-      <c r="B39" s="74" t="str">
-        <f>'Launch Plan'!D81</f>
+      <c r="B39" s="81" t="str">
+        <f>'Launch Plan'!D80</f>
         <v>PWA GATE: ask-vet-assistant rate limiting / abuse protection shipped</v>
       </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
       <c r="L39" s="39" t="str">
-        <f>'Launch Plan'!K81</f>
+        <f>'Launch Plan'!K80</f>
         <v>Not Started</v>
       </c>
       <c r="M39" s="39" t="str">
-        <f>'Launch Plan'!L81</f>
+        <f>'Launch Plan'!L80</f>
         <v>Yes</v>
       </c>
       <c r="N39" s="39" t="str">
@@ -3460,28 +3460,28 @@
     </row>
     <row r="40" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="36" t="str">
-        <f>'Launch Plan'!A113</f>
+        <f>'Launch Plan'!A112</f>
         <v>App Store</v>
       </c>
-      <c r="B40" s="74" t="str">
-        <f>'Launch Plan'!D113</f>
+      <c r="B40" s="81" t="str">
+        <f>'Launch Plan'!D112</f>
         <v>APP STORE GATE: PWA already passed Go/No-Go and ran 21+ consecutive clean usage days</v>
       </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
       <c r="L40" s="39" t="str">
-        <f>'Launch Plan'!K113</f>
+        <f>'Launch Plan'!K112</f>
         <v>Not Started</v>
       </c>
       <c r="M40" s="39" t="str">
-        <f>'Launch Plan'!L113</f>
+        <f>'Launch Plan'!L112</f>
         <v>Yes</v>
       </c>
       <c r="N40" s="39" t="str">
@@ -3491,28 +3491,28 @@
     </row>
     <row r="41" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="36" t="str">
-        <f>'Launch Plan'!A114</f>
+        <f>'Launch Plan'!A113</f>
         <v>App Store</v>
       </c>
-      <c r="B41" s="74" t="str">
-        <f>'Launch Plan'!D114</f>
+      <c r="B41" s="81" t="str">
+        <f>'Launch Plan'!D113</f>
         <v>APP STORE GATE: Business Readiness complete</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="82"/>
+      <c r="K41" s="82"/>
       <c r="L41" s="39" t="str">
-        <f>'Launch Plan'!K114</f>
+        <f>'Launch Plan'!K113</f>
         <v>Not Started</v>
       </c>
       <c r="M41" s="39" t="str">
-        <f>'Launch Plan'!L114</f>
+        <f>'Launch Plan'!L113</f>
         <v>Yes</v>
       </c>
       <c r="N41" s="39" t="str">
@@ -3522,28 +3522,28 @@
     </row>
     <row r="42" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="36" t="str">
-        <f>'Launch Plan'!A115</f>
+        <f>'Launch Plan'!A114</f>
         <v>App Store</v>
       </c>
-      <c r="B42" s="74" t="str">
-        <f>'Launch Plan'!D115</f>
+      <c r="B42" s="81" t="str">
+        <f>'Launch Plan'!D114</f>
         <v>APP STORE GATE: Capacitor builds pass internal testing, no Critical bugs</v>
       </c>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
-      <c r="K42" s="75"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="82"/>
       <c r="L42" s="39" t="str">
-        <f>'Launch Plan'!K115</f>
+        <f>'Launch Plan'!K114</f>
         <v>Not Started</v>
       </c>
       <c r="M42" s="39" t="str">
-        <f>'Launch Plan'!L115</f>
+        <f>'Launch Plan'!L114</f>
         <v>Yes</v>
       </c>
       <c r="N42" s="39" t="str">
@@ -3553,28 +3553,28 @@
     </row>
     <row r="43" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="36" t="str">
-        <f>'Launch Plan'!A116</f>
+        <f>'Launch Plan'!A115</f>
         <v>App Store</v>
       </c>
-      <c r="B43" s="74" t="str">
-        <f>'Launch Plan'!D116</f>
+      <c r="B43" s="81" t="str">
+        <f>'Launch Plan'!D115</f>
         <v>APP STORE GATE: All Requirements items complete for both stores</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
-      <c r="K43" s="75"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="82"/>
+      <c r="I43" s="82"/>
+      <c r="J43" s="82"/>
+      <c r="K43" s="82"/>
       <c r="L43" s="39" t="str">
-        <f>'Launch Plan'!K116</f>
+        <f>'Launch Plan'!K115</f>
         <v>Not Started</v>
       </c>
       <c r="M43" s="39" t="str">
-        <f>'Launch Plan'!L116</f>
+        <f>'Launch Plan'!L115</f>
         <v>Yes</v>
       </c>
       <c r="N43" s="39" t="str">
@@ -3584,28 +3584,28 @@
     </row>
     <row r="44" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="37" t="str">
-        <f>'Launch Plan'!A117</f>
+        <f>'Launch Plan'!A116</f>
         <v>App Store</v>
       </c>
-      <c r="B44" s="86" t="str">
-        <f>'Launch Plan'!D117</f>
+      <c r="B44" s="94" t="str">
+        <f>'Launch Plan'!D116</f>
         <v>APP STORE GATE: Explicit decision recorded — still worth pursuing given PWA results?</v>
       </c>
-      <c r="C44" s="79"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="79"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="79"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
       <c r="L44" s="40" t="str">
-        <f>'Launch Plan'!K117</f>
+        <f>'Launch Plan'!K116</f>
         <v>Not Started</v>
       </c>
       <c r="M44" s="40" t="str">
-        <f>'Launch Plan'!L117</f>
+        <f>'Launch Plan'!L116</f>
         <v>Yes</v>
       </c>
       <c r="N44" s="40" t="str">
@@ -3646,7 +3646,7 @@
       <c r="N46" s="8"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="91" t="s">
         <v>298</v>
       </c>
       <c r="B47" s="69"/>
@@ -3719,19 +3719,19 @@
         <v>16</v>
       </c>
       <c r="C50" s="32">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>8</v>
       </c>
       <c r="D50" s="32">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>8</v>
       </c>
       <c r="E50" s="32">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F50" s="32">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A50,'Launch Plan'!$B$5:$B$127,B50,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A50,'Launch Plan'!$B$5:$B$126,B50,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="G50" s="42">
@@ -3757,19 +3757,19 @@
         <v>56</v>
       </c>
       <c r="C51" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>15</v>
       </c>
       <c r="D51" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>7</v>
       </c>
       <c r="E51" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="F51" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A51,'Launch Plan'!$B$5:$B$127,B51,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A51,'Launch Plan'!$B$5:$B$126,B51,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>7</v>
       </c>
       <c r="G51" s="43">
@@ -3792,22 +3792,22 @@
         <v>15</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C52" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>9</v>
       </c>
       <c r="D52" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E52" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F52" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A52,'Launch Plan'!$B$5:$B$127,B52,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A52,'Launch Plan'!$B$5:$B$126,B52,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>9</v>
       </c>
       <c r="G52" s="43">
@@ -3830,22 +3830,22 @@
         <v>15</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C53" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D53" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E53" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F53" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A53,'Launch Plan'!$B$5:$B$127,B53,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A53,'Launch Plan'!$B$5:$B$126,B53,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G53" s="43">
@@ -3868,22 +3868,22 @@
         <v>15</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C54" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D54" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E54" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F54" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A54,'Launch Plan'!$B$5:$B$127,B54,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A54,'Launch Plan'!$B$5:$B$126,B54,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G54" s="43">
@@ -3909,19 +3909,19 @@
         <v>47</v>
       </c>
       <c r="C55" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>2</v>
       </c>
       <c r="D55" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>2</v>
       </c>
       <c r="E55" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F55" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A55,'Launch Plan'!$B$5:$B$127,B55,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A55,'Launch Plan'!$B$5:$B$126,B55,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="G55" s="43">
@@ -3947,19 +3947,19 @@
         <v>50</v>
       </c>
       <c r="C56" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="D56" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>2</v>
       </c>
       <c r="E56" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F56" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A56,'Launch Plan'!$B$5:$B$127,B56,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A56,'Launch Plan'!$B$5:$B$126,B56,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G56" s="43">
@@ -3985,19 +3985,19 @@
         <v>87</v>
       </c>
       <c r="C57" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D57" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E57" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F57" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A57,'Launch Plan'!$B$5:$B$127,B57,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A57,'Launch Plan'!$B$5:$B$126,B57,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G57" s="43">
@@ -4023,20 +4023,20 @@
         <v>93</v>
       </c>
       <c r="C58" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>2</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>1</v>
       </c>
       <c r="D58" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E58" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F58" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A58,'Launch Plan'!$B$5:$B$127,B58,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>2</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A58,'Launch Plan'!$B$5:$B$126,B58,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>1</v>
       </c>
       <c r="G58" s="43">
         <f t="shared" si="3"/>
@@ -4058,22 +4058,22 @@
         <v>92</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="D59" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E59" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F59" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A59,'Launch Plan'!$B$5:$B$127,B59,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A59,'Launch Plan'!$B$5:$B$126,B59,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="G59" s="43">
@@ -4096,22 +4096,22 @@
         <v>92</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C60" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D60" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E60" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="F60" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A60,'Launch Plan'!$B$5:$B$127,B60,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A60,'Launch Plan'!$B$5:$B$126,B60,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="G60" s="43">
@@ -4134,22 +4134,22 @@
         <v>92</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C61" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D61" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E61" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F61" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A61,'Launch Plan'!$B$5:$B$127,B61,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A61,'Launch Plan'!$B$5:$B$126,B61,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G61" s="43">
@@ -4169,34 +4169,34 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C62" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="D62" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"Complete")</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="33">
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E62" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
-        <v>1</v>
-      </c>
       <c r="F62" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A62,'Launch Plan'!$B$5:$B$127,B62,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A62,'Launch Plan'!$B$5:$B$126,B62,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>2</v>
       </c>
       <c r="G62" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H62" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>MOVING</v>
+        <v>PARTIAL</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -4207,25 +4207,25 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C63" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D63" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E63" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F63" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A63,'Launch Plan'!$B$5:$B$127,B63,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A63,'Launch Plan'!$B$5:$B$126,B63,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G63" s="43">
@@ -4245,25 +4245,25 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C64" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="D64" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E64" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F64" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A64,'Launch Plan'!$B$5:$B$127,B64,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A64,'Launch Plan'!$B$5:$B$126,B64,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="G64" s="43">
@@ -4283,25 +4283,25 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C65" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D65" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E65" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F65" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A65,'Launch Plan'!$B$5:$B$127,B65,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A65,'Launch Plan'!$B$5:$B$126,B65,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G65" s="43">
@@ -4321,25 +4321,25 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C66" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D66" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E66" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F66" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A66,'Launch Plan'!$B$5:$B$127,B66,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A66,'Launch Plan'!$B$5:$B$126,B66,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G66" s="43">
@@ -4359,30 +4359,30 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C67" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>14</v>
       </c>
       <c r="D67" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"Complete")</f>
-        <v>1</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"Complete")</f>
+        <v>2</v>
       </c>
       <c r="E67" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F67" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A67,'Launch Plan'!$B$5:$B$127,B67,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
-        <v>13</v>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A67,'Launch Plan'!$B$5:$B$126,B67,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
+        <v>12</v>
       </c>
       <c r="G67" s="43">
         <f t="shared" si="3"/>
-        <v>7.1428571428571425E-2</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H67" s="33" t="str">
         <f t="shared" si="4"/>
@@ -4397,25 +4397,25 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C68" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>11</v>
       </c>
       <c r="D68" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E68" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F68" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A68,'Launch Plan'!$B$5:$B$127,B68,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A68,'Launch Plan'!$B$5:$B$126,B68,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>11</v>
       </c>
       <c r="G68" s="43">
@@ -4435,25 +4435,25 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C69" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D69" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E69" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F69" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A69,'Launch Plan'!$B$5:$B$127,B69,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A69,'Launch Plan'!$B$5:$B$126,B69,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G69" s="43">
@@ -4473,25 +4473,25 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="33" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C70" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>10</v>
       </c>
       <c r="D70" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E70" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F70" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A70,'Launch Plan'!$B$5:$B$127,B70,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A70,'Launch Plan'!$B$5:$B$126,B70,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>10</v>
       </c>
       <c r="G70" s="43">
@@ -4511,25 +4511,25 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C71" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="D71" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E71" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F71" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A71,'Launch Plan'!$B$5:$B$127,B71,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A71,'Launch Plan'!$B$5:$B$126,B71,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="G71" s="43">
@@ -4549,25 +4549,25 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B72" s="33" t="s">
         <v>56</v>
       </c>
       <c r="C72" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="D72" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E72" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F72" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A72,'Launch Plan'!$B$5:$B$127,B72,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A72,'Launch Plan'!$B$5:$B$126,B72,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>3</v>
       </c>
       <c r="G72" s="43">
@@ -4587,25 +4587,25 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C73" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>8</v>
       </c>
       <c r="D73" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E73" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F73" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A73,'Launch Plan'!$B$5:$B$127,B73,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A73,'Launch Plan'!$B$5:$B$126,B73,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>8</v>
       </c>
       <c r="G73" s="43">
@@ -4625,25 +4625,25 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C74" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="D74" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E74" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F74" s="33">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A74,'Launch Plan'!$B$5:$B$127,B74,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A74,'Launch Plan'!$B$5:$B$126,B74,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="G74" s="43">
@@ -4663,25 +4663,25 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="34" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C75" s="34">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"Complete")+COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"In Progress")+COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="D75" s="34">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"Complete")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"Complete")</f>
         <v>0</v>
       </c>
       <c r="E75" s="34">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"In Progress")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="F75" s="34">
-        <f>COUNTIFS('Launch Plan'!$A$5:$A$127,A75,'Launch Plan'!$B$5:$B$127,B75,'Launch Plan'!$K$5:$K$127,"Not Started")</f>
+        <f>COUNTIFS('Launch Plan'!$A$5:$A$126,A75,'Launch Plan'!$B$5:$B$126,B75,'Launch Plan'!$K$5:$K$126,"Not Started")</f>
         <v>1</v>
       </c>
       <c r="G75" s="44">
@@ -4941,23 +4941,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="B36:K36"/>
-    <mergeCell ref="G6:I8"/>
-    <mergeCell ref="B32:K32"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="M6:N8"/>
-    <mergeCell ref="B31:K31"/>
-    <mergeCell ref="A27:N27"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A6:C8"/>
-    <mergeCell ref="J6:L8"/>
     <mergeCell ref="A47:N47"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="A1:N2"/>
@@ -4974,6 +4957,23 @@
     <mergeCell ref="B43:K43"/>
     <mergeCell ref="B39:K39"/>
     <mergeCell ref="B41:K41"/>
+    <mergeCell ref="G6:I8"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="M6:N8"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A6:C8"/>
+    <mergeCell ref="J6:L8"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="B36:K36"/>
   </mergeCells>
   <conditionalFormatting sqref="G50:G75">
     <cfRule type="dataBar" priority="12">
@@ -5046,7 +5046,7 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" customWidth="1"/>
     <col min="3" max="3" width="12.7265625" customWidth="1"/>
     <col min="4" max="4" width="42" style="57" customWidth="1"/>
     <col min="5" max="5" width="10" hidden="1" customWidth="1"/>
@@ -5124,7 +5124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="51" t="s">
         <v>15</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="54" t="s">
         <v>15</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="54" t="s">
         <v>15</v>
       </c>
@@ -6338,18 +6338,18 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="54" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C34" s="56">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D34" s="60" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E34" s="54" t="s">
         <v>18</v>
@@ -6358,40 +6358,40 @@
         <v>19</v>
       </c>
       <c r="G34" s="54" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H34" s="55">
         <v>46243</v>
       </c>
       <c r="I34" s="56">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J34" s="55">
         <f t="shared" si="0"/>
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="K34" s="54" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="L34" s="54" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="M34" s="54" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B35" s="54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" s="56">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" s="54" t="s">
         <v>18</v>
@@ -6413,10 +6413,10 @@
         <v>46257</v>
       </c>
       <c r="K35" s="54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L35" s="54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M35" s="54" t="s">
         <v>102</v>
@@ -6424,13 +6424,13 @@
     </row>
     <row r="36" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" s="56">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D36" s="60" t="s">
         <v>103</v>
@@ -6458,7 +6458,7 @@
         <v>70</v>
       </c>
       <c r="L36" s="54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M36" s="54" t="s">
         <v>104</v>
@@ -6466,16 +6466,16 @@
     </row>
     <row r="37" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B37" s="54" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C37" s="56">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" s="54" t="s">
         <v>18</v>
@@ -6484,7 +6484,7 @@
         <v>19</v>
       </c>
       <c r="G37" s="54" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H37" s="55">
         <v>46243</v>
@@ -6500,21 +6500,19 @@
         <v>70</v>
       </c>
       <c r="L37" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="M37" s="54" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="M37" s="54"/>
+    </row>
+    <row r="38" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="54" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B38" s="54" t="s">
         <v>107</v>
       </c>
       <c r="C38" s="56">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="60" t="s">
         <v>108</v>
@@ -6526,79 +6524,81 @@
         <v>19</v>
       </c>
       <c r="G38" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H38" s="55">
         <v>46243</v>
       </c>
-      <c r="I38" s="56">
-        <v>14</v>
-      </c>
+      <c r="I38" s="56"/>
       <c r="J38" s="55">
         <f t="shared" si="1"/>
-        <v>46257</v>
+        <v>46243</v>
       </c>
       <c r="K38" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="54" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="M38" s="54"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="54" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B39" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="56">
+        <v>36</v>
+      </c>
+      <c r="D39" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="54" t="s">
         <v>109</v>
-      </c>
-      <c r="C39" s="56">
-        <v>35</v>
-      </c>
-      <c r="D39" s="60" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>18</v>
       </c>
       <c r="F39" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="54" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H39" s="55">
         <v>46243</v>
       </c>
-      <c r="I39" s="56"/>
+      <c r="I39" s="56">
+        <v>21</v>
+      </c>
       <c r="J39" s="55">
         <f t="shared" si="1"/>
-        <v>46243</v>
+        <v>46264</v>
       </c>
       <c r="K39" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="M39" s="54"/>
-    </row>
-    <row r="40" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="M39" s="54" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C40" s="56">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D40" s="60" t="s">
         <v>113</v>
       </c>
       <c r="E40" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F40" s="54" t="s">
         <v>19</v>
@@ -6628,19 +6628,19 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41" s="56">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D41" s="60" t="s">
         <v>115</v>
       </c>
       <c r="E41" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F41" s="54" t="s">
         <v>19</v>
@@ -6670,19 +6670,19 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" s="56">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D42" s="60" t="s">
         <v>117</v>
       </c>
       <c r="E42" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F42" s="54" t="s">
         <v>19</v>
@@ -6710,21 +6710,21 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B43" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C43" s="56">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D43" s="60" t="s">
         <v>119</v>
       </c>
       <c r="E43" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F43" s="54" t="s">
         <v>19</v>
@@ -6752,21 +6752,21 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C44" s="56">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D44" s="60" t="s">
         <v>121</v>
       </c>
       <c r="E44" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F44" s="54" t="s">
         <v>19</v>
@@ -6794,21 +6794,21 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B45" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C45" s="56">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D45" s="60" t="s">
         <v>123</v>
       </c>
       <c r="E45" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F45" s="54" t="s">
         <v>19</v>
@@ -6838,19 +6838,19 @@
     </row>
     <row r="46" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B46" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C46" s="56">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D46" s="60" t="s">
         <v>125</v>
       </c>
       <c r="E46" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F46" s="54" t="s">
         <v>19</v>
@@ -6880,19 +6880,19 @@
     </row>
     <row r="47" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B47" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C47" s="56">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D47" s="60" t="s">
         <v>127</v>
       </c>
       <c r="E47" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F47" s="54" t="s">
         <v>19</v>
@@ -6911,7 +6911,7 @@
         <v>46264</v>
       </c>
       <c r="K47" s="54" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="L47" s="54" t="s">
         <v>90</v>
@@ -6922,19 +6922,19 @@
     </row>
     <row r="48" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B48" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C48" s="56">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D48" s="60" t="s">
         <v>129</v>
       </c>
       <c r="E48" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F48" s="54" t="s">
         <v>19</v>
@@ -6964,25 +6964,25 @@
     </row>
     <row r="49" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B49" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="56">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D49" s="60" t="s">
         <v>131</v>
       </c>
       <c r="E49" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F49" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H49" s="55">
         <v>46243</v>
@@ -7006,19 +7006,19 @@
     </row>
     <row r="50" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B50" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C50" s="56">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D50" s="60" t="s">
         <v>133</v>
       </c>
       <c r="E50" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F50" s="54" t="s">
         <v>19</v>
@@ -7048,19 +7048,19 @@
     </row>
     <row r="51" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B51" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C51" s="56">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D51" s="60" t="s">
         <v>135</v>
       </c>
       <c r="E51" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F51" s="54" t="s">
         <v>19</v>
@@ -7088,21 +7088,21 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B52" s="54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C52" s="56">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D52" s="60" t="s">
         <v>137</v>
       </c>
       <c r="E52" s="54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F52" s="54" t="s">
         <v>19</v>
@@ -7130,21 +7130,21 @@
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="54" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B53" s="54" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C53" s="56">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D53" s="60" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="E53" s="54" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="F53" s="54" t="s">
         <v>19</v>
@@ -7153,37 +7153,37 @@
         <v>39</v>
       </c>
       <c r="H53" s="55">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="I53" s="56">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J53" s="55">
         <f t="shared" si="1"/>
-        <v>46264</v>
+        <v>46255</v>
       </c>
       <c r="K53" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="54" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="M53" s="54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="56">
+        <v>51</v>
+      </c>
+      <c r="D54" s="60" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A54" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" s="56">
-        <v>50</v>
-      </c>
-      <c r="D54" s="60" t="s">
-        <v>57</v>
       </c>
       <c r="E54" s="54" t="s">
         <v>18</v>
@@ -7195,20 +7195,20 @@
         <v>39</v>
       </c>
       <c r="H54" s="55">
-        <v>46250</v>
+        <v>46261</v>
       </c>
       <c r="I54" s="56">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J54" s="55">
         <f t="shared" si="1"/>
-        <v>46255</v>
+        <v>46275</v>
       </c>
       <c r="K54" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="54" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M54" s="54" t="s">
         <v>141</v>
@@ -7216,61 +7216,61 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="54" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C55" s="56">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D55" s="60" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E55" s="54" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="F55" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="54" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H55" s="55">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="I55" s="56">
         <v>14</v>
       </c>
       <c r="J55" s="55">
         <f t="shared" si="1"/>
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="K55" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="54" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="M55" s="54" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B56" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C56" s="56">
+        <v>53</v>
+      </c>
+      <c r="D56" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E56" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C56" s="56">
-        <v>52</v>
-      </c>
-      <c r="D56" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F56" s="54" t="s">
         <v>19</v>
@@ -7295,24 +7295,24 @@
         <v>90</v>
       </c>
       <c r="M56" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B57" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="56">
+        <v>54</v>
+      </c>
+      <c r="D57" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C57" s="56">
-        <v>53</v>
-      </c>
-      <c r="D57" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F57" s="54" t="s">
         <v>19</v>
@@ -7337,24 +7337,24 @@
         <v>90</v>
       </c>
       <c r="M57" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B58" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="56">
+        <v>55</v>
+      </c>
+      <c r="D58" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="E58" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C58" s="56">
-        <v>54</v>
-      </c>
-      <c r="D58" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F58" s="54" t="s">
         <v>19</v>
@@ -7379,24 +7379,24 @@
         <v>90</v>
       </c>
       <c r="M58" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B59" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="56">
+        <v>56</v>
+      </c>
+      <c r="D59" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="E59" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C59" s="56">
-        <v>55</v>
-      </c>
-      <c r="D59" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E59" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F59" s="54" t="s">
         <v>19</v>
@@ -7421,24 +7421,24 @@
         <v>90</v>
       </c>
       <c r="M59" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B60" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="56">
+        <v>57</v>
+      </c>
+      <c r="D60" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C60" s="56">
-        <v>56</v>
-      </c>
-      <c r="D60" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E60" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F60" s="54" t="s">
         <v>19</v>
@@ -7463,24 +7463,24 @@
         <v>90</v>
       </c>
       <c r="M60" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B61" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" s="56">
+        <v>58</v>
+      </c>
+      <c r="D61" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C61" s="56">
-        <v>57</v>
-      </c>
-      <c r="D61" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="E61" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F61" s="54" t="s">
         <v>19</v>
@@ -7505,24 +7505,24 @@
         <v>90</v>
       </c>
       <c r="M61" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B62" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="56">
+        <v>59</v>
+      </c>
+      <c r="D62" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="E62" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C62" s="56">
-        <v>58</v>
-      </c>
-      <c r="D62" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="E62" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F62" s="54" t="s">
         <v>19</v>
@@ -7547,24 +7547,24 @@
         <v>90</v>
       </c>
       <c r="M62" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B63" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" s="56">
+        <v>60</v>
+      </c>
+      <c r="D63" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="E63" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C63" s="56">
-        <v>59</v>
-      </c>
-      <c r="D63" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="E63" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F63" s="54" t="s">
         <v>19</v>
@@ -7589,24 +7589,24 @@
         <v>90</v>
       </c>
       <c r="M63" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B64" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="56">
+        <v>61</v>
+      </c>
+      <c r="D64" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="E64" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C64" s="56">
-        <v>60</v>
-      </c>
-      <c r="D64" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E64" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F64" s="54" t="s">
         <v>19</v>
@@ -7631,24 +7631,24 @@
         <v>90</v>
       </c>
       <c r="M64" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B65" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="56">
+        <v>62</v>
+      </c>
+      <c r="D65" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E65" s="54" t="s">
         <v>145</v>
-      </c>
-      <c r="C65" s="56">
-        <v>61</v>
-      </c>
-      <c r="D65" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" s="54" t="s">
-        <v>147</v>
       </c>
       <c r="F65" s="54" t="s">
         <v>19</v>
@@ -7673,30 +7673,30 @@
         <v>90</v>
       </c>
       <c r="M65" s="54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="54" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C66" s="56">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D66" s="60" t="s">
         <v>158</v>
       </c>
       <c r="E66" s="54" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="F66" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="54" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="H66" s="55">
         <v>46264</v>
@@ -7709,24 +7709,24 @@
         <v>46278</v>
       </c>
       <c r="K66" s="54" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L66" s="54" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="M66" s="54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="54" t="s">
         <v>92</v>
       </c>
       <c r="B67" s="54" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="C67" s="56">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D67" s="60" t="s">
         <v>160</v>
@@ -7751,7 +7751,7 @@
         <v>46278</v>
       </c>
       <c r="K67" s="54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L67" s="54" t="s">
         <v>36</v>
@@ -7760,15 +7760,15 @@
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="54" t="s">
         <v>92</v>
       </c>
       <c r="B68" s="54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C68" s="56">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D68" s="60" t="s">
         <v>162</v>
@@ -7780,7 +7780,7 @@
         <v>19</v>
       </c>
       <c r="G68" s="54" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H68" s="55">
         <v>46264</v>
@@ -7796,21 +7796,21 @@
         <v>70</v>
       </c>
       <c r="L68" s="54" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M68" s="54" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="54" t="s">
         <v>92</v>
       </c>
       <c r="B69" s="54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C69" s="56">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D69" s="60" t="s">
         <v>164</v>
@@ -7840,105 +7840,105 @@
       <c r="L69" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M69" s="54" t="s">
+      <c r="M69" s="54"/>
+    </row>
+    <row r="70" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" s="56">
+        <v>67</v>
+      </c>
+      <c r="D70" s="60" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A70" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="B70" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="56">
-        <v>66</v>
-      </c>
-      <c r="D70" s="60" t="s">
-        <v>166</v>
       </c>
       <c r="E70" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="G70" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H70" s="55">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="I70" s="56">
         <v>14</v>
       </c>
       <c r="J70" s="55">
         <f t="shared" si="2"/>
-        <v>46278</v>
+        <v>46257</v>
       </c>
       <c r="K70" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L70" s="54" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M70" s="54"/>
     </row>
     <row r="71" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="54" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="B71" s="54" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="C71" s="56">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D71" s="60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E71" s="54" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="G71" s="54" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H71" s="55">
-        <v>46243</v>
+        <v>46278</v>
       </c>
       <c r="I71" s="56">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J71" s="55">
         <f t="shared" si="2"/>
-        <v>46257</v>
+        <v>46285</v>
       </c>
       <c r="K71" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L71" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="M71" s="54"/>
-    </row>
-    <row r="72" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="M71" s="54" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="54" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="B72" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="56">
+        <v>69</v>
+      </c>
+      <c r="D72" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" s="54" t="s">
         <v>169</v>
-      </c>
-      <c r="C72" s="56">
-        <v>68</v>
-      </c>
-      <c r="D72" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="E72" s="54" t="s">
-        <v>171</v>
       </c>
       <c r="F72" s="54" t="s">
         <v>19</v>
@@ -7962,25 +7962,23 @@
       <c r="L72" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M72" s="54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M72" s="54"/>
+    </row>
+    <row r="73" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B73" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="56">
+        <v>70</v>
+      </c>
+      <c r="D73" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="C73" s="56">
-        <v>69</v>
-      </c>
-      <c r="D73" s="60" t="s">
-        <v>174</v>
-      </c>
       <c r="E73" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F73" s="54" t="s">
         <v>19</v>
@@ -8006,21 +8004,21 @@
       </c>
       <c r="M73" s="54"/>
     </row>
-    <row r="74" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B74" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C74" s="56">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D74" s="60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E74" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F74" s="54" t="s">
         <v>19</v>
@@ -8046,21 +8044,21 @@
       </c>
       <c r="M74" s="54"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B75" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C75" s="56">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D75" s="60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E75" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F75" s="54" t="s">
         <v>19</v>
@@ -8084,23 +8082,25 @@
       <c r="L75" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M75" s="54"/>
+      <c r="M75" s="54" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="76" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B76" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C76" s="56">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D76" s="60" t="s">
         <v>177</v>
       </c>
       <c r="E76" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="54" t="s">
         <v>19</v>
@@ -8124,25 +8124,23 @@
       <c r="L76" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M76" s="54" t="s">
-        <v>178</v>
-      </c>
+      <c r="M76" s="54"/>
     </row>
     <row r="77" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B77" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C77" s="56">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D77" s="60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E77" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F77" s="54" t="s">
         <v>19</v>
@@ -8168,21 +8166,21 @@
       </c>
       <c r="M77" s="54"/>
     </row>
-    <row r="78" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C78" s="56">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D78" s="60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E78" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F78" s="54" t="s">
         <v>19</v>
@@ -8206,23 +8204,25 @@
       <c r="L78" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M78" s="54"/>
-    </row>
-    <row r="79" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M78" s="54" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B79" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C79" s="56">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D79" s="60" t="s">
         <v>181</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F79" s="54" t="s">
         <v>19</v>
@@ -8255,16 +8255,16 @@
         <v>15</v>
       </c>
       <c r="B80" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C80" s="56">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D80" s="60" t="s">
         <v>183</v>
       </c>
       <c r="E80" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F80" s="54" t="s">
         <v>19</v>
@@ -8292,21 +8292,21 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="54" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="B81" s="54" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C81" s="56">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E81" s="54" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="F81" s="54" t="s">
         <v>19</v>
@@ -8315,34 +8315,34 @@
         <v>20</v>
       </c>
       <c r="H81" s="55">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="I81" s="56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J81" s="55">
         <f t="shared" si="2"/>
-        <v>46285</v>
+        <v>46283</v>
       </c>
       <c r="K81" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L81" s="54" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="M81" s="54" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B82" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C82" s="56">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D82" s="60" t="s">
         <v>189</v>
@@ -8372,22 +8372,20 @@
       <c r="L82" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="M82" s="54" t="s">
+      <c r="M82" s="54"/>
+    </row>
+    <row r="83" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="B83" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" s="56">
+        <v>80</v>
+      </c>
+      <c r="D83" s="60" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A83" s="54" t="s">
-        <v>187</v>
-      </c>
-      <c r="B83" s="54" t="s">
-        <v>188</v>
-      </c>
-      <c r="C83" s="56">
-        <v>79</v>
-      </c>
-      <c r="D83" s="60" t="s">
-        <v>191</v>
       </c>
       <c r="E83" s="54" t="s">
         <v>18</v>
@@ -8396,7 +8394,7 @@
         <v>19</v>
       </c>
       <c r="G83" s="54" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H83" s="55">
         <v>46282</v>
@@ -8416,18 +8414,18 @@
       </c>
       <c r="M83" s="54"/>
     </row>
-    <row r="84" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B84" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C84" s="56">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E84" s="54" t="s">
         <v>18</v>
@@ -8458,16 +8456,16 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B85" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C85" s="56">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E85" s="54" t="s">
         <v>18</v>
@@ -8496,24 +8494,24 @@
       </c>
       <c r="M85" s="54"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B86" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C86" s="56">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D86" s="60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E86" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="G86" s="54" t="s">
         <v>27</v>
@@ -8534,26 +8532,28 @@
       <c r="L86" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="M86" s="54"/>
+      <c r="M86" s="54" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="87" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B87" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C87" s="56">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D87" s="60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E87" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G87" s="54" t="s">
         <v>27</v>
@@ -8578,15 +8578,15 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B88" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C88" s="56">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D88" s="60" t="s">
         <v>198</v>
@@ -8595,7 +8595,7 @@
         <v>18</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>27</v>
@@ -8616,19 +8616,17 @@
       <c r="L88" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="M88" s="54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M88" s="54"/>
+    </row>
+    <row r="89" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B89" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C89" s="56">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D89" s="60" t="s">
         <v>200</v>
@@ -8637,10 +8635,10 @@
         <v>18</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="G89" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H89" s="55">
         <v>46282</v>
@@ -8660,24 +8658,24 @@
       </c>
       <c r="M89" s="54"/>
     </row>
-    <row r="90" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B90" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C90" s="56">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D90" s="60" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E90" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="G90" s="54" t="s">
         <v>39</v>
@@ -8698,20 +8696,22 @@
       <c r="L90" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="M90" s="54"/>
-    </row>
-    <row r="91" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M90" s="54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="54" t="s">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="B91" s="54" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C91" s="56">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D91" s="60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E91" s="54" t="s">
         <v>18</v>
@@ -8720,37 +8720,37 @@
         <v>19</v>
       </c>
       <c r="G91" s="54" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H91" s="55">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="I91" s="56">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J91" s="55">
         <f t="shared" si="2"/>
-        <v>46283</v>
+        <v>46325</v>
       </c>
       <c r="K91" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L91" s="54" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="M91" s="54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B92" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C92" s="56">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D92" s="60" t="s">
         <v>206</v>
@@ -8778,7 +8778,7 @@
         <v>70</v>
       </c>
       <c r="L92" s="54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M92" s="54" t="s">
         <v>207</v>
@@ -8786,13 +8786,13 @@
     </row>
     <row r="93" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B93" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C93" s="56">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D93" s="60" t="s">
         <v>208</v>
@@ -8820,7 +8820,7 @@
         <v>70</v>
       </c>
       <c r="L93" s="54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M93" s="54" t="s">
         <v>209</v>
@@ -8828,16 +8828,16 @@
     </row>
     <row r="94" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B94" s="54" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C94" s="56">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D94" s="60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E94" s="54" t="s">
         <v>18</v>
@@ -8846,7 +8846,7 @@
         <v>19</v>
       </c>
       <c r="G94" s="54" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H94" s="55">
         <v>46295</v>
@@ -8862,24 +8862,24 @@
         <v>70</v>
       </c>
       <c r="L94" s="54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M94" s="54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B95" s="54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C95" s="56">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D95" s="60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E95" s="54" t="s">
         <v>18</v>
@@ -8888,7 +8888,7 @@
         <v>19</v>
       </c>
       <c r="G95" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H95" s="55">
         <v>46295</v>
@@ -8904,33 +8904,33 @@
         <v>70</v>
       </c>
       <c r="L95" s="54" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="M95" s="54" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="54" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="B96" s="54" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C96" s="56">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="60" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E96" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F96" s="54" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G96" s="54" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H96" s="55">
         <v>46295</v>
@@ -8949,18 +8949,18 @@
         <v>22</v>
       </c>
       <c r="M96" s="54" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B97" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C97" s="56">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D97" s="60" t="s">
         <v>220</v>
@@ -8996,13 +8996,13 @@
     </row>
     <row r="98" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B98" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C98" s="56">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D98" s="60" t="s">
         <v>222</v>
@@ -9014,7 +9014,7 @@
         <v>30</v>
       </c>
       <c r="G98" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H98" s="55">
         <v>46295</v>
@@ -9030,21 +9030,21 @@
         <v>70</v>
       </c>
       <c r="L98" s="54" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M98" s="54" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B99" s="54" t="s">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="C99" s="56">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D99" s="60" t="s">
         <v>224</v>
@@ -9053,10 +9053,10 @@
         <v>18</v>
       </c>
       <c r="F99" s="54" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H99" s="55">
         <v>46295</v>
@@ -9072,7 +9072,7 @@
         <v>70</v>
       </c>
       <c r="L99" s="54" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M99" s="54" t="s">
         <v>225</v>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B100" s="54" t="s">
         <v>56</v>
       </c>
       <c r="C100" s="56">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D100" s="60" t="s">
         <v>226</v>
@@ -9116,22 +9116,20 @@
       <c r="L100" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M100" s="54" t="s">
-        <v>227</v>
-      </c>
+      <c r="M100" s="54"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B101" s="54" t="s">
         <v>56</v>
       </c>
       <c r="C101" s="56">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D101" s="60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E101" s="54" t="s">
         <v>18</v>
@@ -9140,7 +9138,7 @@
         <v>19</v>
       </c>
       <c r="G101" s="54" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H101" s="55">
         <v>46295</v>
@@ -9149,7 +9147,7 @@
         <v>30</v>
       </c>
       <c r="J101" s="55">
-        <f t="shared" ref="J101:J127" si="3">H101+I101</f>
+        <f t="shared" ref="J101:J132" si="3">H101+I101</f>
         <v>46325</v>
       </c>
       <c r="K101" s="54" t="s">
@@ -9160,27 +9158,27 @@
       </c>
       <c r="M101" s="54"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="54" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="B102" s="54" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C102" s="56">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D102" s="60" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E102" s="54" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F102" s="54" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="G102" s="54" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="H102" s="55">
         <v>46295</v>
@@ -9193,34 +9191,36 @@
         <v>46325</v>
       </c>
       <c r="K102" s="54" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L102" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="M102" s="54"/>
-    </row>
-    <row r="103" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="M102" s="54" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="54" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="B103" s="54" t="s">
-        <v>87</v>
+        <v>230</v>
       </c>
       <c r="C103" s="56">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E103" s="54" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="F103" s="54" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="G103" s="54" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="H103" s="55">
         <v>46295</v>
@@ -9233,27 +9233,25 @@
         <v>46325</v>
       </c>
       <c r="K103" s="54" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L103" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="M103" s="54" t="s">
-        <v>231</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="M103" s="54"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B104" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" s="56">
+        <v>101</v>
+      </c>
+      <c r="D104" s="60" t="s">
         <v>232</v>
-      </c>
-      <c r="C104" s="56">
-        <v>100</v>
-      </c>
-      <c r="D104" s="60" t="s">
-        <v>233</v>
       </c>
       <c r="E104" s="54" t="s">
         <v>18</v>
@@ -9284,16 +9282,16 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B105" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C105" s="56">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D105" s="60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E105" s="54" t="s">
         <v>18</v>
@@ -9302,7 +9300,7 @@
         <v>19</v>
       </c>
       <c r="G105" s="54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H105" s="55">
         <v>46295</v>
@@ -9318,22 +9316,22 @@
         <v>70</v>
       </c>
       <c r="L105" s="54" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M105" s="54"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B106" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C106" s="56">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E106" s="54" t="s">
         <v>18</v>
@@ -9342,7 +9340,7 @@
         <v>19</v>
       </c>
       <c r="G106" s="54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H106" s="55">
         <v>46295</v>
@@ -9358,22 +9356,22 @@
         <v>70</v>
       </c>
       <c r="L106" s="54" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M106" s="54"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B107" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C107" s="56">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D107" s="60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E107" s="54" t="s">
         <v>18</v>
@@ -9404,16 +9402,16 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B108" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C108" s="56">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D108" s="60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E108" s="54" t="s">
         <v>18</v>
@@ -9422,7 +9420,7 @@
         <v>19</v>
       </c>
       <c r="G108" s="54" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H108" s="55">
         <v>46295</v>
@@ -9440,17 +9438,19 @@
       <c r="L108" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M108" s="54"/>
+      <c r="M108" s="54" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B109" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C109" s="56">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D109" s="60" t="s">
         <v>238</v>
@@ -9462,7 +9462,7 @@
         <v>19</v>
       </c>
       <c r="G109" s="54" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H109" s="55">
         <v>46295</v>
@@ -9478,24 +9478,22 @@
         <v>70</v>
       </c>
       <c r="L109" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="M109" s="54" t="s">
-        <v>239</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M109" s="54"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B110" s="54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C110" s="56">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D110" s="60" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E110" s="54" t="s">
         <v>18</v>
@@ -9504,7 +9502,7 @@
         <v>19</v>
       </c>
       <c r="G110" s="54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H110" s="55">
         <v>46295</v>
@@ -9522,20 +9520,22 @@
       <c r="L110" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="M110" s="54"/>
+      <c r="M110" s="54" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="54" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="B111" s="54" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C111" s="56">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D111" s="60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E111" s="54" t="s">
         <v>18</v>
@@ -9544,7 +9544,7 @@
         <v>19</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H111" s="55">
         <v>46295</v>
@@ -9563,66 +9563,66 @@
         <v>36</v>
       </c>
       <c r="M111" s="54" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="54" t="s">
-        <v>92</v>
+        <v>216</v>
       </c>
       <c r="B112" s="54" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="C112" s="56">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D112" s="60" t="s">
         <v>244</v>
       </c>
       <c r="E112" s="54" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="F112" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H112" s="55">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="I112" s="56">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J112" s="55">
         <f t="shared" si="3"/>
-        <v>46325</v>
+        <v>46327</v>
       </c>
       <c r="K112" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L112" s="54" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M112" s="54" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B113" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C113" s="56">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D113" s="60" t="s">
         <v>246</v>
       </c>
       <c r="E113" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F113" s="54" t="s">
         <v>19</v>
@@ -9646,25 +9646,23 @@
       <c r="L113" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M113" s="54" t="s">
+      <c r="M113" s="54"/>
+    </row>
+    <row r="114" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="B114" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C114" s="56">
+        <v>111</v>
+      </c>
+      <c r="D114" s="60" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A114" s="54" t="s">
-        <v>218</v>
-      </c>
-      <c r="B114" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="C114" s="56">
-        <v>110</v>
-      </c>
-      <c r="D114" s="60" t="s">
-        <v>248</v>
-      </c>
       <c r="E114" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F114" s="54" t="s">
         <v>19</v>
@@ -9692,19 +9690,19 @@
     </row>
     <row r="115" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B115" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C115" s="56">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D115" s="60" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E115" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F115" s="54" t="s">
         <v>19</v>
@@ -9732,19 +9730,19 @@
     </row>
     <row r="116" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B116" s="54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C116" s="56">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D116" s="60" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E116" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F116" s="54" t="s">
         <v>19</v>
@@ -9768,45 +9766,47 @@
       <c r="L116" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M116" s="54"/>
+      <c r="M116" s="54" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="117" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="54" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="B117" s="54" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="C117" s="56">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D117" s="60" t="s">
         <v>251</v>
       </c>
       <c r="E117" s="54" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="G117" s="54" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="H117" s="55">
-        <v>46325</v>
+        <v>46341</v>
       </c>
       <c r="I117" s="56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J117" s="55">
         <f t="shared" si="3"/>
-        <v>46327</v>
+        <v>46342</v>
       </c>
       <c r="K117" s="54" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L117" s="54" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="M117" s="54" t="s">
         <v>252</v>
@@ -9820,7 +9820,7 @@
         <v>87</v>
       </c>
       <c r="C118" s="56">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D118" s="60" t="s">
         <v>253</v>
@@ -9856,19 +9856,19 @@
     </row>
     <row r="119" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="54" t="s">
-        <v>86</v>
+        <v>255</v>
       </c>
       <c r="B119" s="54" t="s">
-        <v>87</v>
+        <v>256</v>
       </c>
       <c r="C119" s="56">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D119" s="60" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E119" s="54" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="F119" s="54" t="s">
         <v>90</v>
@@ -9880,11 +9880,11 @@
         <v>46341</v>
       </c>
       <c r="I119" s="56">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J119" s="55">
         <f t="shared" si="3"/>
-        <v>46342</v>
+        <v>46355</v>
       </c>
       <c r="K119" s="54" t="s">
         <v>90</v>
@@ -9893,24 +9893,24 @@
         <v>90</v>
       </c>
       <c r="M119" s="54" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B120" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="C120" s="56">
+        <v>117</v>
+      </c>
+      <c r="D120" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="E120" s="54" t="s">
         <v>258</v>
-      </c>
-      <c r="C120" s="56">
-        <v>116</v>
-      </c>
-      <c r="D120" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="E120" s="54" t="s">
-        <v>260</v>
       </c>
       <c r="F120" s="54" t="s">
         <v>90</v>
@@ -9940,19 +9940,19 @@
     </row>
     <row r="121" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B121" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C121" s="56">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D121" s="60" t="s">
         <v>262</v>
       </c>
       <c r="E121" s="54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F121" s="54" t="s">
         <v>90</v>
@@ -9982,19 +9982,19 @@
     </row>
     <row r="122" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B122" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C122" s="56">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D122" s="60" t="s">
         <v>264</v>
       </c>
       <c r="E122" s="54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F122" s="54" t="s">
         <v>90</v>
@@ -10024,19 +10024,19 @@
     </row>
     <row r="123" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B123" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C123" s="56">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D123" s="60" t="s">
         <v>266</v>
       </c>
       <c r="E123" s="54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F123" s="54" t="s">
         <v>90</v>
@@ -10066,19 +10066,19 @@
     </row>
     <row r="124" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B124" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C124" s="56">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D124" s="60" t="s">
         <v>268</v>
       </c>
       <c r="E124" s="54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F124" s="54" t="s">
         <v>90</v>
@@ -10097,7 +10097,7 @@
         <v>46355</v>
       </c>
       <c r="K124" s="54" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L124" s="54" t="s">
         <v>90</v>
@@ -10106,57 +10106,57 @@
         <v>269</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="54" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="B125" s="54" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C125" s="56">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D125" s="60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E125" s="54" t="s">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="F125" s="54" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="G125" s="54" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="H125" s="55">
-        <v>46341</v>
+        <v>46243</v>
       </c>
       <c r="I125" s="56">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J125" s="55">
         <f t="shared" si="3"/>
-        <v>46355</v>
+        <v>46248</v>
       </c>
       <c r="K125" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L125" s="54" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="M125" s="54" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B126" s="54" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="C126" s="56">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D126" s="60" t="s">
         <v>273</v>
@@ -10184,49 +10184,49 @@
         <v>70</v>
       </c>
       <c r="L126" s="54" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M126" s="54" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A127" s="54" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="B127" s="54" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="C127" s="56">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D127" s="60" t="s">
         <v>275</v>
       </c>
       <c r="E127" s="54" t="s">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="F127" s="54" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="G127" s="54" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H127" s="55">
-        <v>46243</v>
+        <v>46341</v>
       </c>
       <c r="I127" s="56">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J127" s="55">
         <f t="shared" si="3"/>
-        <v>46248</v>
+        <v>46355</v>
       </c>
       <c r="K127" s="54" t="s">
         <v>70</v>
       </c>
       <c r="L127" s="54" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="M127" s="54" t="s">
         <v>276</v>
@@ -10257,8 +10257,8 @@
         <v>278</v>
       </c>
       <c r="B130" s="49">
-        <f>COUNTA(D5:D125)</f>
-        <v>121</v>
+        <f>COUNTA(D5:D127)</f>
+        <v>123</v>
       </c>
       <c r="C130" s="66"/>
       <c r="D130" s="62"/>
@@ -10277,8 +10277,8 @@
         <v>21</v>
       </c>
       <c r="B131" s="50">
-        <f>COUNTIF(K5:K125,"Complete")</f>
-        <v>20</v>
+        <f>COUNTIF(K5:K127,"Complete")</f>
+        <v>22</v>
       </c>
       <c r="C131" s="67"/>
       <c r="D131" s="62"/>
@@ -10297,8 +10297,8 @@
         <v>279</v>
       </c>
       <c r="B132" s="50">
-        <f>COUNTIFS(L5:L125,"Yes",K5:K125,"&lt;&gt;Complete")</f>
-        <v>34</v>
+        <f>COUNTIFS(L5:L127,"Yes",K5:K127,"&lt;&gt;Complete")</f>
+        <v>35</v>
       </c>
       <c r="C132" s="67"/>
       <c r="D132" s="62"/>
@@ -10317,7 +10317,7 @@
         <v>280</v>
       </c>
       <c r="B133" s="50">
-        <f>COUNTIFS(E5:E125,"GATE",K5:K125,"&lt;&gt;Complete")</f>
+        <f>COUNTIFS(E5:E127,"GATE",K5:K127,"&lt;&gt;Complete")</f>
         <v>15</v>
       </c>
       <c r="C133" s="67"/>
@@ -10336,7 +10336,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:M127">
+  <conditionalFormatting sqref="A5:M126">
     <cfRule type="expression" dxfId="23" priority="38">
       <formula>$E5="GATE"</formula>
     </cfRule>
@@ -10386,17 +10386,17 @@
       <formula>$E5="Reference"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G127">
+  <conditionalFormatting sqref="G5:G126">
     <cfRule type="containsText" dxfId="7" priority="46" operator="containsText" text="Critical"/>
     <cfRule type="containsText" dxfId="6" priority="47" operator="containsText" text="High"/>
     <cfRule type="containsText" dxfId="5" priority="48" operator="containsText" text="Medium"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K127">
+  <conditionalFormatting sqref="K5:K126">
     <cfRule type="containsText" dxfId="4" priority="41" operator="containsText" text="Complete"/>
     <cfRule type="containsText" dxfId="3" priority="42" operator="containsText" text="In Progress"/>
     <cfRule type="containsText" dxfId="2" priority="43" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L127">
+  <conditionalFormatting sqref="L5:L126">
     <cfRule type="containsText" dxfId="1" priority="44" operator="containsText" text="Yes"/>
     <cfRule type="containsText" dxfId="0" priority="45" operator="containsText" text="For App Store"/>
   </conditionalFormatting>
